--- a/TEST streamlit.xlsx
+++ b/TEST streamlit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyrki\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66810C50-28F6-43A7-9272-43DBA64EF0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{047E495F-C992-4168-A54D-9791443CA605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -292,9 +292,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -335,13 +332,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -366,6 +366,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Index"/>
@@ -819,16 +820,16 @@
       <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N2">
-        <v>0.25</v>
-      </c>
-      <c r="O2">
-        <v>0.25</v>
-      </c>
-      <c r="P2">
+      <c r="N2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P2" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -869,16 +870,16 @@
       <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="2">
         <v>0.58333333333333337</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -919,16 +920,16 @@
       <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="2">
         <v>0.5</v>
       </c>
-      <c r="N4">
-        <v>0.25</v>
-      </c>
-      <c r="O4">
+      <c r="N4" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O4" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -969,16 +970,16 @@
       <c r="L5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="2">
         <v>0.5</v>
       </c>
-      <c r="N5">
-        <v>0.25</v>
-      </c>
-      <c r="O5">
-        <v>0.25</v>
-      </c>
-      <c r="P5">
+      <c r="N5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1019,16 +1020,16 @@
       <c r="L6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="N6">
-        <v>0.25</v>
-      </c>
-      <c r="O6">
-        <v>0.25</v>
-      </c>
-      <c r="P6">
+      <c r="N6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O6" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P6" s="2">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1069,16 +1070,16 @@
       <c r="L7" t="s">
         <v>34</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="N7">
-        <v>0.25</v>
-      </c>
-      <c r="O7">
+      <c r="N7" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O7" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="2">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1119,16 +1120,16 @@
       <c r="L8" t="s">
         <v>35</v>
       </c>
-      <c r="M8">
-        <v>0.25</v>
-      </c>
-      <c r="N8">
+      <c r="M8" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N8" s="2">
         <v>0.5</v>
       </c>
-      <c r="O8">
-        <v>0.25</v>
-      </c>
-      <c r="P8">
+      <c r="O8" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1169,16 +1170,16 @@
       <c r="L9" t="s">
         <v>31</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>0.5</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1219,16 +1220,16 @@
       <c r="L10" t="s">
         <v>29</v>
       </c>
-      <c r="M10">
-        <v>0.25</v>
-      </c>
-      <c r="N10">
+      <c r="M10" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1269,16 +1270,16 @@
       <c r="L11" t="s">
         <v>26</v>
       </c>
-      <c r="M11">
-        <v>0.25</v>
-      </c>
-      <c r="N11">
+      <c r="M11" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N11" s="2">
         <v>0.5</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1319,16 +1320,16 @@
       <c r="L12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M12">
-        <v>0.25</v>
-      </c>
-      <c r="N12">
+      <c r="M12" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N12" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="2">
         <v>0.25</v>
       </c>
     </row>
@@ -1369,16 +1370,16 @@
       <c r="L13" t="s">
         <v>26</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N13">
-        <v>0.25</v>
-      </c>
-      <c r="O13">
+      <c r="N13" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O13" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="2">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1419,16 +1420,16 @@
       <c r="L14" t="s">
         <v>33</v>
       </c>
-      <c r="M14">
-        <v>0.25</v>
-      </c>
-      <c r="N14">
+      <c r="M14" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N14" s="2">
         <v>0.16666666666666666</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="2">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="2">
         <v>0.25</v>
       </c>
     </row>
@@ -1469,16 +1470,16 @@
       <c r="L15" t="s">
         <v>26</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="2">
         <v>0.5</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>0</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1519,16 +1520,16 @@
       <c r="L16" t="s">
         <v>27</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N16">
-        <v>0.25</v>
-      </c>
-      <c r="O16">
-        <v>0.25</v>
-      </c>
-      <c r="P16">
+      <c r="N16" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="O16" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="P16" s="2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1569,19 +1570,19 @@
       <c r="L17" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="3">
         <f>+'[1]ESTILO LDZ'!$E$23</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="3">
         <f>+'[1]ESTILO LDZ'!$F$23</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="3">
         <f>+'[1]ESTILO LDZ'!$G$23</f>
         <v>0.25</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="3">
         <f>+'[1]ESTILO LDZ'!$H$23</f>
         <v>0.25</v>
       </c>

--- a/TEST streamlit.xlsx
+++ b/TEST streamlit.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyrki\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jyrki\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{047E495F-C992-4168-A54D-9791443CA605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46134771-1F8B-4B13-B074-A258A2D9B396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="84">
   <si>
     <t>Técnico/Funcional</t>
   </si>
@@ -286,13 +286,31 @@
   </si>
   <si>
     <t>KARLA CLAURE ORTIZ</t>
+  </si>
+  <si>
+    <t>ARIEL FELIX PEDRAZA QUISBERT</t>
+  </si>
+  <si>
+    <t>CESAR PARRAGA CUELLAR</t>
+  </si>
+  <si>
+    <t>Persona  competente y estable, apacible y simpático, tiene capacidades administrativas. Mediador, evita conflictos, trabaja bien bajo presión, busca el camino fácil. Puede presentar problemas para automotivarse, por lo cual requerirá constantemente de un buen orientador y/o supervisor, poco proactivos  y desalenador con los otros.</t>
+  </si>
+  <si>
+    <t>ISFP</t>
+  </si>
+  <si>
+    <t>Los ISPF son amables, considerados, compasivos hacia los más necesitados y tienen una mente abierta y flexible. Atiende a las necesidades de las personas de la organización cuando ascienden. Actúan para garantizar el bienestar de los demás. Infunden alegría en su trabajo. Integran bien las tareas y las personas gracias a su ánimo colaborador. Atienden a los aspectos humanos de la organización.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -307,6 +325,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -332,16 +355,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -383,6 +407,7 @@
       <sheetName val="TEMPRa"/>
       <sheetName val="est"/>
       <sheetName val="INFORME"/>
+      <sheetName val="Hoja1"/>
       <sheetName val="TEMPERAMENTO"/>
       <sheetName val="ANCLAS"/>
       <sheetName val="ESTILO LDZ"/>
@@ -408,26 +433,27 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17">
         <row r="23">
           <cell r="E23">
+            <v>0.58333333333333337</v>
+          </cell>
+          <cell r="F23">
+            <v>0.25</v>
+          </cell>
+          <cell r="G23">
             <v>0.16666666666666666</v>
           </cell>
-          <cell r="F23">
-            <v>0.33333333333333331</v>
-          </cell>
-          <cell r="G23">
-            <v>0.25</v>
-          </cell>
           <cell r="H23">
-            <v>0.25</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -721,7 +747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95243E58-F7BC-4984-8E16-DCB7312BCFEE}">
   <sheetPr codeName="Hoja23"/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
@@ -820,16 +846,16 @@
       <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N2" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P2" s="2">
+      <c r="N2">
+        <v>0.25</v>
+      </c>
+      <c r="O2">
+        <v>0.25</v>
+      </c>
+      <c r="P2">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -870,16 +896,16 @@
       <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>0.58333333333333337</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3">
         <v>0</v>
       </c>
     </row>
@@ -920,16 +946,16 @@
       <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4">
         <v>0.5</v>
       </c>
-      <c r="N4" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O4" s="2">
+      <c r="N4">
+        <v>0.25</v>
+      </c>
+      <c r="O4">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -970,16 +996,16 @@
       <c r="L5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>0.5</v>
       </c>
-      <c r="N5" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P5" s="2">
+      <c r="N5">
+        <v>0.25</v>
+      </c>
+      <c r="O5">
+        <v>0.25</v>
+      </c>
+      <c r="P5">
         <v>0</v>
       </c>
     </row>
@@ -1020,16 +1046,16 @@
       <c r="L6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>0.33333333333333331</v>
       </c>
-      <c r="N6" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P6" s="2">
+      <c r="N6">
+        <v>0.25</v>
+      </c>
+      <c r="O6">
+        <v>0.25</v>
+      </c>
+      <c r="P6">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1070,16 +1096,16 @@
       <c r="L7" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7">
         <v>0.16666666666666666</v>
       </c>
-      <c r="N7" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="N7">
+        <v>0.25</v>
+      </c>
+      <c r="O7">
         <v>0.41666666666666669</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1120,16 +1146,16 @@
       <c r="L8" t="s">
         <v>35</v>
       </c>
-      <c r="M8" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="M8">
+        <v>0.25</v>
+      </c>
+      <c r="N8">
         <v>0.5</v>
       </c>
-      <c r="O8" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P8" s="2">
+      <c r="O8">
+        <v>0.25</v>
+      </c>
+      <c r="P8">
         <v>0</v>
       </c>
     </row>
@@ -1170,16 +1196,16 @@
       <c r="L9" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9">
         <v>0.16666666666666666</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9">
         <v>0.5</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9">
         <v>0</v>
       </c>
     </row>
@@ -1220,16 +1246,16 @@
       <c r="L10" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="M10">
+        <v>0.25</v>
+      </c>
+      <c r="N10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10">
         <v>0</v>
       </c>
     </row>
@@ -1270,16 +1296,16 @@
       <c r="L11" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N11" s="2">
+      <c r="M11">
+        <v>0.25</v>
+      </c>
+      <c r="N11">
         <v>0.5</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1320,16 +1346,16 @@
       <c r="L12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N12" s="2">
+      <c r="M12">
+        <v>0.25</v>
+      </c>
+      <c r="N12">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12">
         <v>0.25</v>
       </c>
     </row>
@@ -1370,16 +1396,16 @@
       <c r="L13" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N13" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O13" s="2">
+      <c r="N13">
+        <v>0.25</v>
+      </c>
+      <c r="O13">
         <v>0.16666666666666666</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13">
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -1420,16 +1446,16 @@
       <c r="L14" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N14" s="2">
+      <c r="M14">
+        <v>0.25</v>
+      </c>
+      <c r="N14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14">
         <v>0.25</v>
       </c>
     </row>
@@ -1470,16 +1496,16 @@
       <c r="L15" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15">
         <v>0.5</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1520,16 +1546,16 @@
       <c r="L16" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16">
         <v>0.41666666666666669</v>
       </c>
-      <c r="N16" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O16" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P16" s="2">
+      <c r="N16">
+        <v>0.25</v>
+      </c>
+      <c r="O16">
+        <v>0.25</v>
+      </c>
+      <c r="P16">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -1570,21 +1596,121 @@
       <c r="L17" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="2">
         <f>+'[1]ESTILO LDZ'!$E$23</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="N17" s="2">
+        <f>+'[1]ESTILO LDZ'!$F$23</f>
+        <v>0.25</v>
+      </c>
+      <c r="O17" s="2">
+        <f>+'[1]ESTILO LDZ'!$G$23</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="N17" s="3">
-        <f>+'[1]ESTILO LDZ'!$F$23</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O17" s="3">
-        <f>+'[1]ESTILO LDZ'!$G$23</f>
-        <v>0.25</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="2">
         <f>+'[1]ESTILO LDZ'!$H$23</f>
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N18">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O18">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M19">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="N19">
+        <v>0.25</v>
+      </c>
+      <c r="O19">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
